--- a/data/trans_orig/P36B09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B09-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de carne en 2007</t>
+          <t>Población según la frecuencia de consumo de carne en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>964</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>20358</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42253</t>
+          <t>40816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>24191</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15902</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>36266</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>54028</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>42003</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>70290</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24191</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15234</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34614</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>54028</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>42165</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>69146</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199335</t>
+          <t>200951</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>248719</t>
+          <t>247096</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>252245</t>
+          <t>251892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>304275</t>
+          <t>302600</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>467957</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>538554</t>
+          <t>538149</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>309837</t>
+          <t>314268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>362130</t>
+          <t>364899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>337561</t>
+          <t>339151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>390502</t>
+          <t>390072</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>666815</t>
+          <t>664140</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>740172</t>
+          <t>739606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,54%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81559</t>
+          <t>80151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117359</t>
+          <t>115655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32453</t>
+          <t>31589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98551</t>
+          <t>98539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139938</t>
+          <t>141199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>20875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10379</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28715</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24781</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48222</t>
+          <t>47483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35267</t>
+          <t>35149</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64284</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67586</t>
+          <t>68119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102101</t>
+          <t>104219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>347300</t>
+          <t>348635</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>411809</t>
+          <t>411331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>414724</t>
+          <t>412196</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>475281</t>
+          <t>477744</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>776311</t>
+          <t>782057</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>870964</t>
+          <t>868572</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>431620</t>
+          <t>434610</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>498109</t>
+          <t>497808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>403373</t>
+          <t>400959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>462657</t>
+          <t>465374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>856735</t>
+          <t>848857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>945282</t>
+          <t>940459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57753</t>
+          <t>57585</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93436</t>
+          <t>93089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20822</t>
+          <t>20515</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44170</t>
+          <t>43904</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83986</t>
+          <t>87060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128539</t>
+          <t>126955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18795</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33381</t>
+          <t>33494</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39181</t>
+          <t>39971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24219</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47059</t>
+          <t>45924</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48803</t>
+          <t>47962</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79299</t>
+          <t>78998</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>289130</t>
+          <t>289618</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>341193</t>
+          <t>341954</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>316165</t>
+          <t>315188</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>366063</t>
+          <t>367413</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>621279</t>
+          <t>619585</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>691176</t>
+          <t>693127</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>261509</t>
+          <t>260204</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>312784</t>
+          <t>313133</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>255772</t>
+          <t>254505</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>306050</t>
+          <t>306788</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>530901</t>
+          <t>529638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>602739</t>
+          <t>602605</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,26%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>27014</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52496</t>
+          <t>51698</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28010</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>41509</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70560</t>
+          <t>71664</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>19458</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11979</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31203</t>
+          <t>31942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>21854</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44497</t>
+          <t>44400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34503</t>
+          <t>34044</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60992</t>
+          <t>59596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>51408</t>
+          <t>52305</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>84638</t>
+          <t>83753</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>92041</t>
+          <t>92150</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>134170</t>
+          <t>135590</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>366398</t>
+          <t>359201</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>425278</t>
+          <t>419550</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>442278</t>
+          <t>445524</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>508892</t>
+          <t>512410</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>828649</t>
+          <t>826205</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>917005</t>
+          <t>911377</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,03%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>402079</t>
+          <t>407099</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>464177</t>
+          <t>464189</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>390379</t>
+          <t>388488</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>451995</t>
+          <t>454166</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>809091</t>
+          <t>813307</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>896753</t>
+          <t>894335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46070</t>
+          <t>45493</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77362</t>
+          <t>76812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40151</t>
+          <t>40383</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71414</t>
+          <t>69860</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91598</t>
+          <t>92597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>135824</t>
+          <t>137186</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41415</t>
+          <t>41723</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32421</t>
+          <t>32642</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57505</t>
+          <t>59839</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56012</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>91752</t>
+          <t>93821</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>115668</t>
+          <t>115669</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>160949</t>
+          <t>161179</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147356</t>
+          <t>147757</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>201444</t>
+          <t>199549</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>277365</t>
+          <t>275597</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>348635</t>
+          <t>344688</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1262175</t>
+          <t>1260944</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1372920</t>
+          <t>1366734</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1482745</t>
+          <t>1475639</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1595043</t>
+          <t>1595229</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2769798</t>
+          <t>2778495</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2938413</t>
+          <t>2933484</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1467319</t>
+          <t>1465369</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1582388</t>
+          <t>1574589</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1441320</t>
+          <t>1439496</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1556047</t>
+          <t>1555289</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2931400</t>
+          <t>2939492</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3102581</t>
+          <t>3100994</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>236423</t>
+          <t>241293</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>300293</t>
+          <t>307633</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>103632</t>
+          <t>103036</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>149515</t>
+          <t>146338</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>356301</t>
+          <t>357909</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>435253</t>
+          <t>432843</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de carne en 2012</t>
+          <t>Población según la frecuencia de consumo de carne en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>13637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,82 +4389,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9773</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5064</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17580</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>16828</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>9944</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>26390</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>1,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9773</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4344</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18296</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>16828</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>9834</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>26256</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48527</t>
+          <t>48722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82384</t>
+          <t>80541</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59847</t>
+          <t>59406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93167</t>
+          <t>94989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115673</t>
+          <t>115796</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162399</t>
+          <t>163568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>255392</t>
+          <t>255116</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>307004</t>
+          <t>307461</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>262571</t>
+          <t>262913</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>316742</t>
+          <t>314601</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>531817</t>
+          <t>534172</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>607404</t>
+          <t>607210</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>260167</t>
+          <t>258819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>315534</t>
+          <t>314338</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>260485</t>
+          <t>257724</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>311322</t>
+          <t>311763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>535506</t>
+          <t>537031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>610996</t>
+          <t>609882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47380</t>
+          <t>48300</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80471</t>
+          <t>80218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>26238</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50877</t>
+          <t>49862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81018</t>
+          <t>80371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120417</t>
+          <t>120022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>19224</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51291</t>
+          <t>50493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83653</t>
+          <t>84194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81630</t>
+          <t>83539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121054</t>
+          <t>121616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139797</t>
+          <t>142757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>189709</t>
+          <t>193378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>350301</t>
+          <t>353153</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415568</t>
+          <t>414894</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>394947</t>
+          <t>393311</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>459697</t>
+          <t>459937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>764215</t>
+          <t>764063</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>852194</t>
+          <t>856596</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>456260</t>
+          <t>457985</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>521634</t>
+          <t>521841</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>378825</t>
+          <t>379634</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>441112</t>
+          <t>445381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>851317</t>
+          <t>854708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>942222</t>
+          <t>946742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54198</t>
+          <t>53805</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88676</t>
+          <t>88318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67335</t>
+          <t>66485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105340</t>
+          <t>101875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128853</t>
+          <t>131128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177956</t>
+          <t>182559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20937</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34057</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26650</t>
+          <t>26599</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56001</t>
+          <t>54571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>43428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74028</t>
+          <t>75112</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75592</t>
+          <t>78371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>116915</t>
+          <t>117926</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>270783</t>
+          <t>269327</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>326201</t>
+          <t>327820</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>324722</t>
+          <t>325179</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>381778</t>
+          <t>383390</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>607070</t>
+          <t>606855</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>690822</t>
+          <t>689727</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>312198</t>
+          <t>316213</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>372205</t>
+          <t>375160</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>285487</t>
+          <t>282383</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341140</t>
+          <t>340477</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>615401</t>
+          <t>619381</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>695361</t>
+          <t>703358</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49396</t>
+          <t>48535</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80818</t>
+          <t>82493</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27824</t>
+          <t>28586</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54235</t>
+          <t>55005</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85707</t>
+          <t>82439</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125211</t>
+          <t>124543</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>21630</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27907</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17450</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40791</t>
+          <t>42553</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55507</t>
+          <t>55920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88933</t>
+          <t>91043</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>75268</t>
+          <t>75371</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>112198</t>
+          <t>113802</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>139844</t>
+          <t>139775</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>187686</t>
+          <t>189543</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>339708</t>
+          <t>339155</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>400516</t>
+          <t>400544</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>447400</t>
+          <t>450326</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>514317</t>
+          <t>514044</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>801521</t>
+          <t>807569</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>895291</t>
+          <t>896080</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>389679</t>
+          <t>384643</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>451191</t>
+          <t>447989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>371235</t>
+          <t>370900</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>435215</t>
+          <t>433277</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>777816</t>
+          <t>776903</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>867358</t>
+          <t>864060</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60690</t>
+          <t>61735</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>94552</t>
+          <t>93751</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>40487</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70798</t>
+          <t>69427</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>111834</t>
+          <t>110938</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>153543</t>
+          <t>155630</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19765</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44400</t>
+          <t>45855</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32312</t>
+          <t>32569</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60578</t>
+          <t>61319</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>58290</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>95969</t>
+          <t>95937</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>209360</t>
+          <t>207917</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>272089</t>
+          <t>268866</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>291363</t>
+          <t>294458</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>359157</t>
+          <t>364528</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>516409</t>
+          <t>518438</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>613176</t>
+          <t>612087</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1272133</t>
+          <t>1269666</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1386665</t>
+          <t>1389440</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1490080</t>
+          <t>1482025</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1610682</t>
+          <t>1604925</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2797879</t>
+          <t>2797175</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2957050</t>
+          <t>2971043</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1477538</t>
+          <t>1480254</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1600302</t>
+          <t>1601214</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1351798</t>
+          <t>1352546</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1469086</t>
+          <t>1471188</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2871879</t>
+          <t>2867035</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3034613</t>
+          <t>3039873</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>240621</t>
+          <t>241455</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>305685</t>
+          <t>304185</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>186134</t>
+          <t>187255</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>244236</t>
+          <t>246200</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>441476</t>
+          <t>442699</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>527555</t>
+          <t>532301</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de carne en 2016</t>
+          <t>Población según la frecuencia de consumo de carne en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42126</t>
+          <t>44310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>37835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66313</t>
+          <t>67477</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>224290</t>
+          <t>223099</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>277087</t>
+          <t>275146</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>261855</t>
+          <t>263261</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313155</t>
+          <t>314780</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>503261</t>
+          <t>503688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>575832</t>
+          <t>574438</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>292547</t>
+          <t>297576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>346237</t>
+          <t>351061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>252426</t>
+          <t>253653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>303328</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>561584</t>
+          <t>563088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>637784</t>
+          <t>632754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57959</t>
+          <t>56956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88918</t>
+          <t>88802</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50924</t>
+          <t>50277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82126</t>
+          <t>79361</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115402</t>
+          <t>115663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161255</t>
+          <t>158812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>23018</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26298</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28353</t>
+          <t>28545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24391</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47902</t>
+          <t>48440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39766</t>
+          <t>38425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70805</t>
+          <t>70789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>342870</t>
+          <t>345560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>407642</t>
+          <t>407763</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>386960</t>
+          <t>388339</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>451848</t>
+          <t>449152</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>751002</t>
+          <t>750657</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>847174</t>
+          <t>841990</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>419916</t>
+          <t>421857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>483747</t>
+          <t>484569</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>381807</t>
+          <t>382424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>445528</t>
+          <t>446894</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>820910</t>
+          <t>821835</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>913441</t>
+          <t>911606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,23%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145160</t>
+          <t>147064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193394</t>
+          <t>194287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138011</t>
+          <t>138630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184071</t>
+          <t>185326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>299567</t>
+          <t>297316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364312</t>
+          <t>365237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20321</t>
+          <t>21970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>19682</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43361</t>
+          <t>43074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23711</t>
+          <t>23724</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47895</t>
+          <t>47236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>49226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80636</t>
+          <t>83721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>180019</t>
+          <t>178195</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>229872</t>
+          <t>228092</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>225501</t>
+          <t>222233</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>277166</t>
+          <t>274683</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>416839</t>
+          <t>418545</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>490150</t>
+          <t>491955</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>333759</t>
+          <t>336155</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>390035</t>
+          <t>389794</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>297310</t>
+          <t>300768</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>351751</t>
+          <t>353394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>652383</t>
+          <t>649068</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>729029</t>
+          <t>732447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133151</t>
+          <t>132873</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179752</t>
+          <t>176847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>146479</t>
+          <t>146484</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193422</t>
+          <t>192264</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>289097</t>
+          <t>289567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>356602</t>
+          <t>356645</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18937</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>22320</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34448</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22764</t>
+          <t>21995</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44732</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35886</t>
+          <t>37129</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65152</t>
+          <t>64957</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63937</t>
+          <t>63898</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99896</t>
+          <t>100512</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>301230</t>
+          <t>301949</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>358668</t>
+          <t>359083</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>422989</t>
+          <t>417150</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>485400</t>
+          <t>484585</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>741019</t>
+          <t>740184</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>831375</t>
+          <t>829029</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>434618</t>
+          <t>435416</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>497345</t>
+          <t>498373</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>386691</t>
+          <t>384988</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>451304</t>
+          <t>452197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>836970</t>
+          <t>831686</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>923090</t>
+          <t>926103</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78272</t>
+          <t>77843</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>116048</t>
+          <t>116038</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>87657</t>
+          <t>88309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>127736</t>
+          <t>129349</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>174731</t>
+          <t>176769</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>232345</t>
+          <t>231403</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32307</t>
+          <t>31665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30490</t>
+          <t>29324</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>58320</t>
+          <t>55617</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49141</t>
+          <t>48983</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>81650</t>
+          <t>82752</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80980</t>
+          <t>80934</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>122087</t>
+          <t>122518</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>124575</t>
+          <t>124179</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175325</t>
+          <t>175162</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>217615</t>
+          <t>215334</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>279235</t>
+          <t>280222</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1103333</t>
+          <t>1106802</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1214894</t>
+          <t>1221646</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1350090</t>
+          <t>1354338</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1480497</t>
+          <t>1473212</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2489925</t>
+          <t>2483423</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2647675</t>
+          <t>2654060</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1541426</t>
+          <t>1544042</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1659365</t>
+          <t>1660146</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1376363</t>
+          <t>1378480</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1497743</t>
+          <t>1492190</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2961191</t>
+          <t>2954753</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3127481</t>
+          <t>3125624</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>449979</t>
+          <t>450929</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>535913</t>
+          <t>535064</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>457742</t>
+          <t>453416</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>539424</t>
+          <t>539922</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>931709</t>
+          <t>932145</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1049983</t>
+          <t>1048022</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B09-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40816</t>
+          <t>41127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15902</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36266</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>41954</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70290</t>
+          <t>71145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>200951</t>
+          <t>200071</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>247096</t>
+          <t>250537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>251892</t>
+          <t>252030</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>302600</t>
+          <t>301399</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>466898</t>
+          <t>467630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>538149</t>
+          <t>537597</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>314268</t>
+          <t>312904</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>364899</t>
+          <t>366152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>339151</t>
+          <t>339500</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>390072</t>
+          <t>388060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>664140</t>
+          <t>665710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>739606</t>
+          <t>739340</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,52%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80151</t>
+          <t>79290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115655</t>
+          <t>118061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>14245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31589</t>
+          <t>31938</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>98822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141199</t>
+          <t>140253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>27547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47483</t>
+          <t>48100</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35149</t>
+          <t>36555</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62274</t>
+          <t>63627</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68119</t>
+          <t>65862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104219</t>
+          <t>102063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>348635</t>
+          <t>349230</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>411331</t>
+          <t>412968</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>412196</t>
+          <t>412281</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>477744</t>
+          <t>474776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>782057</t>
+          <t>778282</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>868572</t>
+          <t>868970</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>434610</t>
+          <t>431579</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>497808</t>
+          <t>494770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>400959</t>
+          <t>400941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>465374</t>
+          <t>463873</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>848857</t>
+          <t>849838</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>940459</t>
+          <t>943971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57585</t>
+          <t>59446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93089</t>
+          <t>93703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20515</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43904</t>
+          <t>44430</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87060</t>
+          <t>85895</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126955</t>
+          <t>128513</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18291</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>19645</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13136</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33494</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18340</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39971</t>
+          <t>39294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>24367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45924</t>
+          <t>46386</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47962</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78998</t>
+          <t>77711</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>289618</t>
+          <t>288795</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>341954</t>
+          <t>345066</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>315188</t>
+          <t>316020</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>367413</t>
+          <t>364393</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>619585</t>
+          <t>622369</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>693127</t>
+          <t>699588</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,38%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>260204</t>
+          <t>259631</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>313133</t>
+          <t>313022</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>254505</t>
+          <t>257948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>306788</t>
+          <t>307078</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>529638</t>
+          <t>529093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>602605</t>
+          <t>604143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27014</t>
+          <t>26948</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51698</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10263</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>26667</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41509</t>
+          <t>42009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71664</t>
+          <t>71039</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31942</t>
+          <t>30697</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44400</t>
+          <t>44993</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34044</t>
+          <t>33969</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59596</t>
+          <t>59962</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52305</t>
+          <t>51305</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83753</t>
+          <t>84756</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>92150</t>
+          <t>91728</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>135590</t>
+          <t>132766</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>359201</t>
+          <t>362955</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>419550</t>
+          <t>423479</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>445524</t>
+          <t>450979</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>512410</t>
+          <t>515260</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>826205</t>
+          <t>824754</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>911377</t>
+          <t>915736</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>407099</t>
+          <t>404235</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>464189</t>
+          <t>465407</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>388488</t>
+          <t>388148</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>454166</t>
+          <t>448522</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>813307</t>
+          <t>810312</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>894335</t>
+          <t>897204</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45493</t>
+          <t>46368</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76812</t>
+          <t>75806</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40383</t>
+          <t>40853</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69860</t>
+          <t>70264</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92597</t>
+          <t>93482</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137186</t>
+          <t>135890</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41723</t>
+          <t>42088</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32642</t>
+          <t>31570</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>59839</t>
+          <t>59394</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>57683</t>
+          <t>57383</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93821</t>
+          <t>91798</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>115669</t>
+          <t>115978</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>161179</t>
+          <t>162677</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147757</t>
+          <t>149260</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>199549</t>
+          <t>199485</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>275597</t>
+          <t>277076</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>344688</t>
+          <t>343763</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1260944</t>
+          <t>1257220</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1366734</t>
+          <t>1367907</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1475639</t>
+          <t>1472361</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1595229</t>
+          <t>1595481</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2778495</t>
+          <t>2773517</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2933484</t>
+          <t>2935532</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1465369</t>
+          <t>1464474</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1574589</t>
+          <t>1577905</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1439496</t>
+          <t>1442695</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1555289</t>
+          <t>1557350</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2939492</t>
+          <t>2939485</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3100994</t>
+          <t>3103091</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,66%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>241293</t>
+          <t>236684</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>307633</t>
+          <t>301058</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>103036</t>
+          <t>103143</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>146338</t>
+          <t>147498</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>357909</t>
+          <t>355208</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>432843</t>
+          <t>428049</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>17565</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26390</t>
+          <t>27478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48722</t>
+          <t>47029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80541</t>
+          <t>81630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>60072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94989</t>
+          <t>92966</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115796</t>
+          <t>117059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163568</t>
+          <t>164733</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>255116</t>
+          <t>252513</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>307461</t>
+          <t>308408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>262913</t>
+          <t>264836</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>314601</t>
+          <t>315738</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>534172</t>
+          <t>533587</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>607210</t>
+          <t>608428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>258819</t>
+          <t>261474</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>314338</t>
+          <t>315638</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>257724</t>
+          <t>257419</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>311763</t>
+          <t>309222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>537031</t>
+          <t>535095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>609882</t>
+          <t>611073</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48300</t>
+          <t>47688</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80218</t>
+          <t>79740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26238</t>
+          <t>26558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49862</t>
+          <t>50132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80371</t>
+          <t>80471</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120022</t>
+          <t>118932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16388</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19224</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50493</t>
+          <t>50106</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84194</t>
+          <t>82850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83539</t>
+          <t>82083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121616</t>
+          <t>123119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142757</t>
+          <t>140217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193378</t>
+          <t>192060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>353153</t>
+          <t>352562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>414894</t>
+          <t>415685</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>393311</t>
+          <t>390843</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>459937</t>
+          <t>459550</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>764063</t>
+          <t>764490</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>856596</t>
+          <t>855130</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>457985</t>
+          <t>456265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>521841</t>
+          <t>521322</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>379634</t>
+          <t>378256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>445381</t>
+          <t>445431</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>854708</t>
+          <t>851363</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>946742</t>
+          <t>944510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53805</t>
+          <t>53508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88318</t>
+          <t>88176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66485</t>
+          <t>65979</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101875</t>
+          <t>104026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131128</t>
+          <t>130641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182559</t>
+          <t>178945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20373</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>32275</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54571</t>
+          <t>55512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43428</t>
+          <t>43317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75112</t>
+          <t>74098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78371</t>
+          <t>78022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117926</t>
+          <t>120227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>269327</t>
+          <t>267045</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>327820</t>
+          <t>324380</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>325179</t>
+          <t>324380</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>383390</t>
+          <t>380407</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>606855</t>
+          <t>605891</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>689727</t>
+          <t>690877</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>316213</t>
+          <t>315140</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>375160</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>282383</t>
+          <t>285370</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>340477</t>
+          <t>342745</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>619381</t>
+          <t>616929</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>703358</t>
+          <t>702007</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48535</t>
+          <t>48242</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82493</t>
+          <t>80277</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28586</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55005</t>
+          <t>53717</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82439</t>
+          <t>84356</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124543</t>
+          <t>126473</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21630</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28252</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>17985</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42553</t>
+          <t>42166</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55920</t>
+          <t>56167</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91043</t>
+          <t>88715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>75371</t>
+          <t>73753</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>113802</t>
+          <t>111443</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>139775</t>
+          <t>140558</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>189543</t>
+          <t>189700</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>339155</t>
+          <t>339418</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>400544</t>
+          <t>401987</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>450326</t>
+          <t>448780</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>514044</t>
+          <t>513537</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>807569</t>
+          <t>805460</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>896080</t>
+          <t>892283</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>384643</t>
+          <t>387517</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>447989</t>
+          <t>451485</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>370900</t>
+          <t>372097</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>433277</t>
+          <t>436010</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>776903</t>
+          <t>777207</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>864060</t>
+          <t>865013</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61735</t>
+          <t>61458</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93751</t>
+          <t>95276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40487</t>
+          <t>41172</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69427</t>
+          <t>71359</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>110938</t>
+          <t>110312</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>155630</t>
+          <t>154500</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20214</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45855</t>
+          <t>44942</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32569</t>
+          <t>32452</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61319</t>
+          <t>60482</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>58290</t>
+          <t>59199</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>95937</t>
+          <t>96227</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>207917</t>
+          <t>209514</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>268866</t>
+          <t>269027</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>294458</t>
+          <t>292078</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>364528</t>
+          <t>362559</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>518438</t>
+          <t>519934</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>612087</t>
+          <t>615389</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1269666</t>
+          <t>1265984</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1389440</t>
+          <t>1388982</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1482025</t>
+          <t>1487047</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1604925</t>
+          <t>1611844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2797175</t>
+          <t>2790658</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2971043</t>
+          <t>2964533</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1480254</t>
+          <t>1480214</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1601214</t>
+          <t>1609718</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1352546</t>
+          <t>1342376</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1471188</t>
+          <t>1465490</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2867035</t>
+          <t>2869786</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3039873</t>
+          <t>3037109</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,66%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>241455</t>
+          <t>239899</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>304185</t>
+          <t>305445</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>187255</t>
+          <t>185776</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>246200</t>
+          <t>244766</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>442699</t>
+          <t>446027</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>532301</t>
+          <t>534497</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20924</t>
+          <t>21056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30805</t>
+          <t>33002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21009</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>44092</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37835</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67477</t>
+          <t>66664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>223099</t>
+          <t>225067</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>275146</t>
+          <t>274953</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>263261</t>
+          <t>262809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>314780</t>
+          <t>311763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>503688</t>
+          <t>506405</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>574438</t>
+          <t>574236</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>297576</t>
+          <t>298222</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>351061</t>
+          <t>348280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>253653</t>
+          <t>252256</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>303688</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>563088</t>
+          <t>564006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>632754</t>
+          <t>636402</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56956</t>
+          <t>57080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88802</t>
+          <t>88118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>49544</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79361</t>
+          <t>80335</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115663</t>
+          <t>116347</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158812</t>
+          <t>159745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>23951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>26372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28545</t>
+          <t>28785</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23009</t>
+          <t>24414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48440</t>
+          <t>49454</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38425</t>
+          <t>39833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70789</t>
+          <t>71798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>345560</t>
+          <t>347076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>407763</t>
+          <t>406746</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>388339</t>
+          <t>385149</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>449152</t>
+          <t>450337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>750657</t>
+          <t>752950</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>841990</t>
+          <t>841359</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>421857</t>
+          <t>420601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>484569</t>
+          <t>484286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382424</t>
+          <t>385064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>446894</t>
+          <t>446519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>821835</t>
+          <t>818950</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>911606</t>
+          <t>913948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147064</t>
+          <t>147533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194287</t>
+          <t>195387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138630</t>
+          <t>137152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>185326</t>
+          <t>186248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297316</t>
+          <t>296190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>365237</t>
+          <t>361566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15864</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43074</t>
+          <t>44026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47236</t>
+          <t>46740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49226</t>
+          <t>49487</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83721</t>
+          <t>81931</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178195</t>
+          <t>178581</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>228092</t>
+          <t>229400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>222233</t>
+          <t>221826</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>274683</t>
+          <t>274707</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>418545</t>
+          <t>416922</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>491955</t>
+          <t>491013</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>336155</t>
+          <t>333893</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>389794</t>
+          <t>390397</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>300768</t>
+          <t>299949</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>353394</t>
+          <t>355388</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>649068</t>
+          <t>645931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>732447</t>
+          <t>731011</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132873</t>
+          <t>131659</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176847</t>
+          <t>178906</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>146484</t>
+          <t>144916</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>192264</t>
+          <t>193587</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>289567</t>
+          <t>290931</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>356645</t>
+          <t>356526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>18075</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22320</t>
+          <t>21299</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>13915</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34474</t>
+          <t>34958</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21995</t>
+          <t>22510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45010</t>
+          <t>45428</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>35929</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>64957</t>
+          <t>64532</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63898</t>
+          <t>63378</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100512</t>
+          <t>99215</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>301949</t>
+          <t>302195</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>359083</t>
+          <t>357937</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>417150</t>
+          <t>422787</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>484585</t>
+          <t>488368</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>740184</t>
+          <t>737425</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>829029</t>
+          <t>828199</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>435416</t>
+          <t>434224</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>498373</t>
+          <t>493494</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>384988</t>
+          <t>386729</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>452197</t>
+          <t>450227</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>831686</t>
+          <t>837175</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>926103</t>
+          <t>926889</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77843</t>
+          <t>79075</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>116038</t>
+          <t>114755</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>88309</t>
+          <t>88327</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>129349</t>
+          <t>131233</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>176769</t>
+          <t>177985</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>231403</t>
+          <t>231589</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13306</t>
+          <t>13653</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31665</t>
+          <t>32594</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>55617</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>48983</t>
+          <t>48527</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>82752</t>
+          <t>82062</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80934</t>
+          <t>81473</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>122518</t>
+          <t>123422</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>124179</t>
+          <t>124896</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175162</t>
+          <t>173705</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>215334</t>
+          <t>217529</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>280222</t>
+          <t>282865</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1106802</t>
+          <t>1101920</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1221646</t>
+          <t>1221677</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1354338</t>
+          <t>1354798</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1473212</t>
+          <t>1475415</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2483423</t>
+          <t>2490495</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2654060</t>
+          <t>2659125</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1544042</t>
+          <t>1542626</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1660146</t>
+          <t>1666645</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1378480</t>
+          <t>1376604</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1492190</t>
+          <t>1492678</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2954753</t>
+          <t>2960074</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3125624</t>
+          <t>3120934</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>450929</t>
+          <t>452041</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>535064</t>
+          <t>535647</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>453416</t>
+          <t>456804</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>539922</t>
+          <t>543880</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>932145</t>
+          <t>933053</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1048022</t>
+          <t>1047742</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
